--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/XRF/Panel 02/front/xrf_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/XRF/Panel 02/front/xrf_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.62321</v>
+        <v>17.96002</v>
       </c>
       <c r="D2" t="n">
-        <v>17.52472</v>
+        <v>17.50949</v>
       </c>
       <c r="E2" t="n">
-        <v>17.53482</v>
+        <v>17.88877</v>
       </c>
       <c r="F2" t="n">
-        <v>45.21452</v>
+        <v>44.10063</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05418</v>
+        <v>0.05377</v>
       </c>
       <c r="H2" t="n">
-        <v>1.91445</v>
+        <v>1.94695</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.97871</v>
+        <v>17.74387</v>
       </c>
       <c r="D3" t="n">
-        <v>18.01941</v>
+        <v>17.69872</v>
       </c>
       <c r="E3" t="n">
-        <v>17.66879</v>
+        <v>17.73273</v>
       </c>
       <c r="F3" t="n">
-        <v>44.59326</v>
+        <v>44.44204</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05382</v>
+        <v>0.05337</v>
       </c>
       <c r="H3" t="n">
-        <v>1.93495</v>
+        <v>1.95373</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.67457</v>
+        <v>17.99488</v>
       </c>
       <c r="D4" t="n">
-        <v>17.554</v>
+        <v>17.13864</v>
       </c>
       <c r="E4" t="n">
-        <v>17.3609</v>
+        <v>17.82541</v>
       </c>
       <c r="F4" t="n">
-        <v>44.51128</v>
+        <v>44.58853</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05382</v>
+        <v>0.0539</v>
       </c>
       <c r="H4" t="n">
-        <v>1.94832</v>
+        <v>1.94303</v>
       </c>
     </row>
   </sheetData>
